--- a/stories/arbres/TREE-FAM-002.xlsx
+++ b/stories/arbres/TREE-FAM-002.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara est au bord de la mer, avec maman. Papa prépare une surprise gentille. C'est bientôt l'anniversaire. On garde un peu. Puis on dit. Maman dit : c'est une surprise gentille.</t>
+          <t>Sara est au bord de la mer, avec maman. Papa prépare une surprise gentille. C'est bientôt l'anniversaire. On garde un peu. Puis on dit. C'est une surprise gentille.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sara est au bord de la mer, avec maman. Papa prépare une surprise gentille. C'est bientôt l'anniversaire. On garde un peu. Puis on dit.
+maman|C'est une surprise gentille.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1677,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Sara aide maman. Papa cache un galet peint. C'est une surprise gentille. On la garde un peu, puis on dit. Sara chuchote : plus tard, on dira.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|C'est une surprise gentille ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. C'est une surprise gentille. Puis on dit. Sara respire. Maman est là. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la cuisine, Sara cache le ballon rouge. C'est une surprise gentille. On la garde un peu, puis on dit. Maman montre le geste, lentement. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2584,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le matin. Puis la cuisine. Puis le ballon rouge. L'eau coule, tout petit bruit. Sara pose la cuisine à sa place. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sara s'arrête près de le seau bleu. la cuisine est rangé. On entend un oiseau. Sara range la tasse. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sara se souvient de le matin. Et de la cuisine. Et de le doudou. On rit un peu. Sara pose sa tête un moment. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3615,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Dans la cuisine, Sara cache le seau bleu. C'est une surprise gentille. On la garde un peu, puis on dit. Maman dit : je suis là. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
+          <t>Dans la cuisine, Sara cache le seau bleu. C'est une surprise gentille. On la garde un peu, puis on dit. Je suis là. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3753,12 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la cuisine, Sara cache le seau bleu. C'est une surprise gentille. On la garde un peu, puis on dit.
+maman|Je suis là. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3945,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4112,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le ballon rouge. Après le jardin. Près de le matin. Sara s'arrête. Un ballon s'immobilise. Sara essuie ses mains. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4279,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4446,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sara range le jardin. le seau bleu reste près de le matin. Le vent est doux. Sara enfile ses chaussons. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4613,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4523,7 +4642,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>le doudou est là. le jardin aussi. le matin reste dans le souvenir. On écoute jusqu'au bout. Sara plie un pull. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+          <t>Le doudou est là. le jardin aussi. le matin reste dans le souvenir. On écoute jusqu'au bout. Sara plie un pull. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4661,6 +4780,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou est là. le jardin aussi. le matin reste dans le souvenir. On écoute jusqu'au bout. Sara plie un pull. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4947,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5114,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la cuisine, Sara cache le doudou. C'est une surprise gentille. On la garde un peu, puis on dit. Maman reste tout près. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5305,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5472,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le ballon rouge. la chambre est rangé. le matin est fini. Un ruban reste dans la poche. Sara range le matin dans sa tête, comme un souvenir. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5639,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5806,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le seau bleu. Sara pose la chambre. le matin est derrière. Un vélo passe au loin. Sara serre la main de maman. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5973,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6140,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sara montre le doudou. Maman a vu le matin. Et la chambre. Les chaussures font toc toc. Sara marche près de maman. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6307,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6336,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Sara se réveille. Maman dit : on garde encore un peu. C'est une surprise gentille. Puis on dit. Le vent est doux. Papa fait un clin d'œil.</t>
+          <t>C'est après la sieste. Sara se réveille. On garde encore un peu. C'est une surprise gentille. Puis on dit. Le vent est doux. Papa fait un clin d'œil.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6474,13 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Sara se réveille.
+maman|On garde encore un peu. C'est une surprise gentille.
+narrateur|Puis on dit. Le vent est doux. Papa fait un clin d'œil.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6661,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On la garde un peu, puis on dit ?</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6834,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. C'est une surprise gentille. Puis on dit. Sara retient le geste. Maman sourit. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7025,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6863,7 +7054,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Dans le jardin, Sara cache le ballon rouge sous un linge. C'est une surprise gentille. Puis on dit. Maman dit : je suis là. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
+          <t>Dans le jardin, Sara cache le ballon rouge sous un linge. C'est une surprise gentille. Puis on dit. Je suis là. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7001,6 +7192,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le jardin, Sara cache le ballon rouge sous un linge. C'est une surprise gentille. Puis on dit.
+maman|Je suis là. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7384,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7551,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi après la sieste. Puis la cuisine. Puis le ballon rouge. Un galet est encore chaud. Sara ferme la porte, tout doux. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7718,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7885,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sara s'arrête près de le seau bleu. la cuisine est rangé. Un linge sèche à l'air. Sara raccroche un linge. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8052,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8219,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sara se souvient de après la sieste. Et de la cuisine. Et de le doudou. Une feuille tombe. Sara montre le doudou à maman. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8386,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8553,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le jardin, Sara cache le seau bleu sous un linge. C'est une surprise gentille. Puis on dit. Maman reste tout près. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8744,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8911,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le ballon rouge. Après le jardin. Près de après la sieste. Sara s'arrête. Une tasse cliquette. Sara répète tout bas le geste. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9078,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9245,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sara range le jardin. le seau bleu reste près de après la sieste. Un crochet tient bien le manteau. Sara tend le seau bleu à papa. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9412,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9179,7 +9441,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>le doudou est là. le jardin aussi. après la sieste reste dans le souvenir. Ça sent le pain chaud. Sara caresse le doudou. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+          <t>Le doudou est là. le jardin aussi. après la sieste reste dans le souvenir. Ça sent le pain chaud. Sara caresse le doudou. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9317,6 +9579,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou est là. le jardin aussi. après la sieste reste dans le souvenir. Ça sent le pain chaud. Sara caresse le doudou. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9746,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9913,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le jardin, Sara cache le doudou sous un linge. C'est une surprise gentille. Puis on dit. Maman montre le geste, lentement. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10104,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9851,7 +10133,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le ballon rouge. la chambre est rangé. après la sieste est fini. Un chat miaule une fois. Sara dit : j'ai appris. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+          <t>Sara rejoint le ballon rouge. la chambre est rangé. après la sieste est fini. Un chat miaule une fois. J'ai appris. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9989,6 +10271,13 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le ballon rouge. la chambre est rangé. après la sieste est fini. Un chat miaule une fois.
+enfant-f|J'ai appris. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu.
+narrateur|Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10440,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10607,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le seau bleu. Sara pose la chambre. après la sieste est derrière. On range un objet. Sara ferme le sac. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10774,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10941,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sara montre le doudou. Maman a vu après la sieste. Et la chambre. On dit merci. Sara prend la main de maman. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11108,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10961,6 +11275,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Sara et maman préparent. C'est une surprise gentille. On la garde un peu, puis on dit. Papa va entendre bientôt. Sara range un ruban.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11460,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Après la surprise gentille, on fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11633,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. C'est une surprise gentille. Puis on dit. Sara hoche la tête. On continue, avec maman. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11824,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11991,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la chambre, Sara pose le ballon rouge sur le lit. C'est une surprise gentille. On la garde un peu, puis on dit. Maman reste tout près. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12182,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12349,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le soir. Puis la cuisine. Puis le ballon rouge. La couverture est douce. Sara sourit. Maman sourit aussi. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12516,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12683,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sara s'arrête près de le seau bleu. la cuisine est rangé. Le savon sent bon. Papa n'est pas loin. Sara les rejoint. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12850,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13017,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sara se souvient de le soir. Et de la cuisine. Et de le doudou. Il y a des miettes sur la table. Sara s'assoit près de maman. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13184,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13351,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la chambre, Sara pose le seau bleu près du lit. C'est une surprise gentille. On la garde un peu, puis on dit. Maman montre le geste, lentement. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13542,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13325,6 +13709,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le ballon rouge. Après le jardin. Près de le soir. Sara s'arrête. On se tient la main. Sara souffle, puis sourit à maman. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13876,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14043,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sara range le jardin. le seau bleu reste près de le soir. On souffle doucement. Sara écoute maman encore une fois. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14210,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13835,7 +14239,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>le doudou est là. le jardin aussi. le soir reste dans le souvenir. La lumière est claire. Sara boit une gorgée d'eau. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+          <t>Le doudou est là. le jardin aussi. le soir reste dans le souvenir. La lumière est claire. Sara boit une gorgée d'eau. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13973,6 +14377,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou est là. le jardin aussi. le soir reste dans le souvenir. La lumière est claire. Sara boit une gorgée d'eau. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14544,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14159,7 +14573,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Dans la chambre, Sara pose le doudou sur l'oreiller. C'est une surprise gentille. On la garde un peu, puis on dit. Maman dit : je suis là. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
+          <t>Dans la chambre, Sara pose le doudou sur l'oreiller. C'est une surprise gentille. On la garde un peu, puis on dit. Je suis là. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14297,6 +14711,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la chambre, Sara pose le doudou sur l'oreiller. C'est une surprise gentille. On la garde un peu, puis on dit.
+maman|Je suis là. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14903,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15070,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le ballon rouge. la chambre est rangé. le soir est fini. Le sol est un peu froid. Sara dit merci à maman. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15237,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15404,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le seau bleu. Sara pose la chambre. le soir est derrière. On attend son tour. Sara chuchote : c'est fini. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15571,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15738,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sara montre le doudou. Maman a vu le soir. Et la chambre. Un panier est posé sur le banc. Sara range encore un peu, près de maman. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15905,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15490,6 +15945,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-FAM-002.xlsx
+++ b/stories/arbres/TREE-FAM-002.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 maman|C'est une surprise gentille.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
           <t>narrateur|C'est le matin. Sara aide maman. Papa cache un galet peint. C'est une surprise gentille. On la garde un peu, puis on dit. Sara chuchote : plus tard, on dira.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|C'est une surprise gentille ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. C'est une surprise gentille. Puis on dit. Sara respire. Maman est là. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Dans la cuisine, Sara cache le ballon rouge. C'est une surprise gentille. On la garde un peu, puis on dit. Maman montre le geste, lentement. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Sara a choisi le matin. Puis la cuisine. Puis le ballon rouge. L'eau coule, tout petit bruit. Sara pose la cuisine à sa place. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Sara s'arrête près de le seau bleu. la cuisine est rangé. On entend un oiseau. Sara range la tasse. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Sara se souvient de le matin. Et de la cuisine. Et de le doudou. On rit un peu. Sara pose sa tête un moment. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3759,6 +3778,7 @@
 maman|Je suis là. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3950,6 +3970,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4117,6 +4138,7 @@
           <t>narrateur|Avec le ballon rouge. Après le jardin. Près de le matin. Sara s'arrête. Un ballon s'immobilise. Sara essuie ses mains. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4284,6 +4306,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4451,6 +4474,7 @@
           <t>narrateur|Sara range le jardin. le seau bleu reste près de le matin. Le vent est doux. Sara enfile ses chaussons. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4618,6 +4642,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4785,6 +4810,7 @@
           <t>narrateur|Le doudou est là. le jardin aussi. le matin reste dans le souvenir. On écoute jusqu'au bout. Sara plie un pull. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4952,6 +4978,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5119,6 +5146,7 @@
           <t>narrateur|Dans la cuisine, Sara cache le doudou. C'est une surprise gentille. On la garde un peu, puis on dit. Maman reste tout près. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5310,6 +5338,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5477,6 +5506,7 @@
           <t>narrateur|Sara rejoint le ballon rouge. la chambre est rangé. le matin est fini. Un ruban reste dans la poche. Sara range le matin dans sa tête, comme un souvenir. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5644,6 +5674,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5811,6 +5842,7 @@
           <t>narrateur|Près de le seau bleu. Sara pose la chambre. le matin est derrière. Un vélo passe au loin. Sara serre la main de maman. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5978,6 +6010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6145,6 +6178,7 @@
           <t>narrateur|Sara montre le doudou. Maman a vu le matin. Et la chambre. Les chaussures font toc toc. Sara marche près de maman. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6312,6 +6346,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6481,6 +6516,7 @@
 narrateur|Puis on dit. Le vent est doux. Papa fait un clin d'œil.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6668,6 +6704,7 @@
           <t>narrateur|On la garde un peu, puis on dit ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6839,6 +6876,7 @@
           <t>narrateur|Oui. C'est une surprise gentille. Puis on dit. Sara retient le geste. Maman sourit. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7030,6 +7068,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7198,6 +7237,7 @@
 maman|Je suis là. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7389,6 +7429,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7556,6 +7597,7 @@
           <t>narrateur|Sara a choisi après la sieste. Puis la cuisine. Puis le ballon rouge. Un galet est encore chaud. Sara ferme la porte, tout doux. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7723,6 +7765,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7890,6 +7933,7 @@
           <t>narrateur|Sara s'arrête près de le seau bleu. la cuisine est rangé. Un linge sèche à l'air. Sara raccroche un linge. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8057,6 +8101,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8224,6 +8269,7 @@
           <t>narrateur|Sara se souvient de après la sieste. Et de la cuisine. Et de le doudou. Une feuille tombe. Sara montre le doudou à maman. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8391,6 +8437,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8558,6 +8605,7 @@
           <t>narrateur|Dans le jardin, Sara cache le seau bleu sous un linge. C'est une surprise gentille. Puis on dit. Maman reste tout près. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8749,6 +8797,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8916,6 +8965,7 @@
           <t>narrateur|Avec le ballon rouge. Après le jardin. Près de après la sieste. Sara s'arrête. Une tasse cliquette. Sara répète tout bas le geste. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9083,6 +9133,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9250,6 +9301,7 @@
           <t>narrateur|Sara range le jardin. le seau bleu reste près de après la sieste. Un crochet tient bien le manteau. Sara tend le seau bleu à papa. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9417,6 +9469,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9584,6 +9637,7 @@
           <t>narrateur|Le doudou est là. le jardin aussi. après la sieste reste dans le souvenir. Ça sent le pain chaud. Sara caresse le doudou. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9751,6 +9805,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9918,6 +9973,7 @@
           <t>narrateur|Dans le jardin, Sara cache le doudou sous un linge. C'est une surprise gentille. Puis on dit. Maman montre le geste, lentement. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10109,6 +10165,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10278,6 +10335,7 @@
 narrateur|Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10445,6 +10503,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10612,6 +10671,7 @@
           <t>narrateur|Près de le seau bleu. Sara pose la chambre. après la sieste est derrière. On range un objet. Sara ferme le sac. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10779,6 +10839,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10946,6 +11007,7 @@
           <t>narrateur|Sara montre le doudou. Maman a vu après la sieste. Et la chambre. On dit merci. Sara prend la main de maman. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11113,6 +11175,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11280,6 +11343,7 @@
           <t>narrateur|C'est le soir. Sara et maman préparent. C'est une surprise gentille. On la garde un peu, puis on dit. Papa va entendre bientôt. Sara range un ruban.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11467,6 +11531,7 @@
           <t>narrateur|Après la surprise gentille, on fait quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11638,6 +11703,7 @@
           <t>narrateur|Oui. C'est une surprise gentille. Puis on dit. Sara hoche la tête. On continue, avec maman. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11829,6 +11895,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11996,6 +12063,7 @@
           <t>narrateur|Dans la chambre, Sara pose le ballon rouge sur le lit. C'est une surprise gentille. On la garde un peu, puis on dit. Maman reste tout près. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12187,6 +12255,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12354,6 +12423,7 @@
           <t>narrateur|Sara a choisi le soir. Puis la cuisine. Puis le ballon rouge. La couverture est douce. Sara sourit. Maman sourit aussi. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12521,6 +12591,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12688,6 +12759,7 @@
           <t>narrateur|Sara s'arrête près de le seau bleu. la cuisine est rangé. Le savon sent bon. Papa n'est pas loin. Sara les rejoint. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12855,6 +12927,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13022,6 +13095,7 @@
           <t>narrateur|Sara se souvient de le soir. Et de la cuisine. Et de le doudou. Il y a des miettes sur la table. Sara s'assoit près de maman. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13189,6 +13263,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13356,6 +13431,7 @@
           <t>narrateur|Dans la chambre, Sara pose le seau bleu près du lit. C'est une surprise gentille. On la garde un peu, puis on dit. Maman montre le geste, lentement. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13547,6 +13623,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13714,6 +13791,7 @@
           <t>narrateur|Avec le ballon rouge. Après le jardin. Près de le soir. Sara s'arrête. On se tient la main. Sara souffle, puis sourit à maman. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13881,6 +13959,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14048,6 +14127,7 @@
           <t>narrateur|Sara range le jardin. le seau bleu reste près de le soir. On souffle doucement. Sara écoute maman encore une fois. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14215,6 +14295,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14382,6 +14463,7 @@
           <t>narrateur|Le doudou est là. le jardin aussi. le soir reste dans le souvenir. La lumière est claire. Sara boit une gorgée d'eau. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14549,6 +14631,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14717,6 +14800,7 @@
 maman|Je suis là. C'est une surprise gentille. On la garde un peu, puis on dit.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14908,6 +14992,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15075,6 +15160,7 @@
           <t>narrateur|Sara rejoint le ballon rouge. la chambre est rangé. le soir est fini. Le sol est un peu froid. Sara dit merci à maman. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15242,6 +15328,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15409,6 +15496,7 @@
           <t>narrateur|Près de le seau bleu. Sara pose la chambre. le soir est derrière. On attend son tour. Sara chuchote : c'est fini. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15576,6 +15664,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15743,6 +15832,7 @@
           <t>narrateur|Sara montre le doudou. Maman a vu le soir. Et la chambre. Un panier est posé sur le banc. Sara range encore un peu, près de maman. C'est une surprise gentille. On la garde un peu, puis on dit. On garde un peu. Puis on dit. C'est une surprise gentille. Sara dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15910,6 +16000,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15928,7 +16019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15952,6 +16043,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15966,7 +16071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16153,6 +16258,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
